--- a/Resources/Doc/SmartDesk测试用例.xlsx
+++ b/Resources/Doc/SmartDesk测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SmartDesk\Resources\zbackup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SmartDesk\Resources\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD94703-6DC1-4625-8AAF-2A11283118C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D83888-C227-4CA5-9AEB-3A4045267FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="576" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="576" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="菜单栏" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="在线文档" sheetId="10" r:id="rId8"/>
     <sheet name="文件下载" sheetId="11" r:id="rId9"/>
     <sheet name="剪切板" sheetId="12" r:id="rId10"/>
+    <sheet name="个人网盘" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="827">
   <si>
     <t>用例编号</t>
   </si>
@@ -2407,6 +2408,280 @@
   <si>
     <t>1.选中某一项
 2.按下Ctrl+Q快捷键</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 用例编号 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 项目名称 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 用例名称 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 前置条件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 测试步骤 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 预期结果 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 网盘管理 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 查看文件列表 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 网盘应用已启动 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 上传文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 拖拽上传文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下载文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 创建文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 进入文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-007 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 重命名文件/文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 删除文件/文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 刷新文件列表 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 点击「刷新」按钮 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 查看下载历史 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 查看下载历史表格 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 查看上传历史 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 查看上传历史表格 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 清空历史记录 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 面包屑导航 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 点击面包屑导航中的上级文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 操作失败处理 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PD-015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 批量操作 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 本地存在测试文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 点击「上传文件」按钮
+2. 选择本地测试文件
+3. 等待上传完成 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 上传成功提示
+2. 文件出现在网盘文件列表中
+3. 上传历史记录更新 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 从本地文件管理器拖拽文件到网盘文件列表区域
+2. 等待上传完成 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 网盘中存在文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 双击需要下载的文件
+2. 等待下载完成 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 下载成功提示
+2. 文件保存到设置的下载目录
+3. 下载历史记录更新 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 点击「新建文件夹」按钮
+2. 输入文件夹名称
+3. 点击确定 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 文件夹创建成功提示
+2. 新文件夹出现在文件列表中 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 网盘中存在文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 双击文件夹
+2. 查看文件列表 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 进入文件夹成功
+2. 显示文件夹内的文件列表
+3. 面包屑导航更新 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 网盘中存在文件或文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 右键点击文件或文件夹
+2. 选择重命名选项
+3. 输入新名称
+4. 点击确定 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 重命名成功提示
+2. 文件或文件夹显示新名称 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 打开网盘应用
+2. 等待文件列表加载 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 文件列表显示正常
+2. 显示文件名称、大小、上传时间等信息 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 右键点击文件或文件夹
+2. 选择删除选项
+3. 确认删除 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 删除成功提示
+2. 文件或文件夹从列表中消失 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 文件列表重新加载
+2. 显示最新的文件状态 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 有下载历史记录 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 显示下载历史记录
+2. 包含文件名、大小、下载时间、保存路径、状态等信息 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 有上传历史记录 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 显示上传历史记录
+2. 包含文件名、大小、上传时间、本地路径、状态等信息 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 有历史记录 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 点击「清空历史」按钮
+2. 确认清空 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 历史记录清空成功
+2. 历史表格为空 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 进入子文件夹 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 成功返回上级文件夹
+2. 文件列表更新
+3. 面包屑导航更新 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 模拟网络异常情况
+2. 执行上传或下载操作 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 显示操作失败提示
+2. 历史记录中状态显示失败 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 网盘应用已启动
+2. 网盘中存在多个文件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 选择多个文件
+2. 执行删除操作 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 所有选择的文件被删除
+2. 显示删除成功提示 </t>
   </si>
 </sst>
 </file>
@@ -2498,7 +2773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2521,6 +2796,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3545,6 +3826,338 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C142FA9-4531-4EF5-ACD7-737647732854}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="21.9140625" defaultRowHeight="75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>826</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H20"/>
@@ -6830,7 +7443,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="27.75" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
@@ -7154,7 +7767,6 @@
     <row r="24" spans="10:12" x14ac:dyDescent="0.3">
       <c r="K24" s="4"/>
     </row>
-    <row r="36" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
